--- a/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour éteindre. L'écran devient noir. Maman sourit. Maman dit : tu peux prendre un autre jeu. Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive. Il dit : tu as su éteindre. Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
+          <t>Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour éteindre. L'écran devient noir. Maman sourit. Tu peux prendre un autre jeu. Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive. Tu as su éteindre. Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour éteindre. L'écran devient noir. Maman sourit.
+maman|Tu peux prendre un autre jeu.
+narrateur|Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive.
+narrateur|Tu as su éteindre.
+narrateur|Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Barbara ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Barbara a su éteindre. Elle a choisi un autre jeu. Maman, l'adulte, a dit fini.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Barbara pose une dernière pièce. Papa range la tablette.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Maman dit fini. Que fait Barbara ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Barbara a su éteindre. Elle a choisi un autre jeu. Maman, l'adulte, a dit fini.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Barbara pose une dernière pièce. Papa range la tablette.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barbara éteint et prend un puzzle</t>
+          <t>Le puzzle en bois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La soupe sent le potiron. Maman dit fini. Sarah éteint. Elle prend le puzzle en bois. Plus tard, les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour éteindre. L'écran devient noir. Maman sourit. Tu peux prendre un autre jeu. Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive. Tu as su éteindre. Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
+          <t>La soupe sent le potiron. L'odeur vient de la cuisine. Une horloge fait tic, tac. Une couverture jaune attend sur le canapé. Le tapis est un peu rêche. Dehors, le vent pousse une feuille. La feuille tape à la vitre. Un bol de bois sèche près de l'horloge. Sarah, tu sens la soupe ? Oui, maman. Ça sent le chaud. En ce moment, Sarah tient la tablette. Les couleurs dansent sur l'écran. Elles sont rouges, puis bleues. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Sarah entend. C'est fini. On va éteindre. Sarah va éteindre. Sarah éteint l'écran. L'écran devient noir. Bravo, Sarah. Tu as éteint. Tu peux prendre un autre jeu. Un autre jeu. Sarah choisit le puzzle en bois. Les pièces sentent le bois. Elles sont lisses et tièdes. Ça sent le bois. Oui. On cherche l'arbre ? Sarah cherche l'arbre. La pièce est verte. Elle rentre. Tu as su éteindre. Bravo. Papa arrive du couloir. Ses chaussettes font un bruit doux. Une pièce rentre. Bien. La pièce est à sa place. Et la maison ? La maison. La maison rentre aussi. Tu ranges la tablette ? Sarah pose la tablette. Elle continue le puzzle. Plus tard, le puzzle est fini. Fini. L'adulte dit fini, encore. On prend un autre jeu. Sarah prend les cubes. Les cubes sont rouges et bleus. Les cubes. Oui. Un autre jeu, c'est bien. Tu as fait du bon travail. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour éteindre. L'écran devient noir. Maman sourit.
+          <t>narrateur|La soupe sent le potiron.
+narrateur|L'odeur vient de la cuisine.
+narrateur|Une horloge fait tic, tac.
+narrateur|Une couverture jaune attend sur le canapé.
+narrateur|Le tapis est un peu rêche.
+narrateur|Dehors, le vent pousse une feuille.
+narrateur|La feuille tape à la vitre.
+narrateur|Un bol de bois sèche près de l'horloge.
+maman|Sarah, tu sens la soupe ?
+enfant-f|Oui, maman.
+enfant-f|Ça sent le chaud.
+narrateur|En ce moment, Sarah tient la tablette.
+narrateur|Les couleurs dansent sur l'écran.
+narrateur|Elles sont rouges, puis bleues.
+narrateur|Maman s'assoit près d'elle.
+maman|Fini.
+narrateur|L'adulte dit fini.
+narrateur|Sarah entend.
+enfant-f|C'est fini.
+maman|On va éteindre.
+narrateur|Sarah va éteindre.
+narrateur|Sarah éteint l'écran.
+narrateur|L'écran devient noir.
+maman|Bravo, Sarah.
+maman|Tu as éteint.
 maman|Tu peux prendre un autre jeu.
-narrateur|Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive.
-narrateur|Tu as su éteindre.
-narrateur|Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.</t>
+enfant-f|Un autre jeu.
+narrateur|Sarah choisit le puzzle en bois.
+narrateur|Les pièces sentent le bois.
+narrateur|Elles sont lisses et tièdes.
+enfant-f|Ça sent le bois.
+maman|Oui.
+maman|On cherche l'arbre ?
+narrateur|Sarah cherche l'arbre.
+narrateur|La pièce est verte.
+narrateur|Elle rentre.
+papa|Tu as su éteindre.
+papa|Bravo.
+narrateur|Papa arrive du couloir.
+narrateur|Ses chaussettes font un bruit doux.
+narrateur|Une pièce rentre.
+papa|Bien.
+papa|La pièce est à sa place.
+maman|Et la maison ?
+enfant-f|La maison.
+narrateur|La maison rentre aussi.
+maman|Tu ranges la tablette ?
+narrateur|Sarah pose la tablette.
+narrateur|Elle continue le puzzle.
+narrateur|Plus tard, le puzzle est fini.
+papa|Fini.
+narrateur|L'adulte dit fini, encore.
+papa|On prend un autre jeu.
+narrateur|Sarah prend les cubes.
+narrateur|Les cubes sont rouges et bleus.
+enfant-f|Les cubes.
+papa|Oui.
+papa|Un autre jeu, c'est bien.
+maman|Tu as fait du bon travail.
+narrateur|La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>soupe</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman dit fini. Que fait Barbara ?</t>
+          <t>Maman dit fini. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman dit fini. Que fait Barbara ?</t>
+          <t>narrateur|Maman dit fini.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Barbara a su éteindre. Elle a choisi un autre jeu. Maman, l'adulte, a dit fini.</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Sarah a éteint. Elle a choisi un autre jeu. Tu as éteint l'écran ? Oui, maman. Et après ? Un autre jeu. Bravo. Le puzzle, c'était bien. Sarah touche une pièce de bois. Le bois est lisse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1744,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Barbara a su éteindre. Elle a choisi un autre jeu. Maman, l'adulte, a dit fini.</t>
+          <t>narrateur|Maman a dit fini.
+narrateur|L'adulte a dit fini.
+narrateur|Sarah a éteint.
+narrateur|Elle a choisi un autre jeu.
+maman|Tu as éteint l'écran ?
+enfant-f|Oui, maman.
+papa|Et après ?
+enfant-f|Un autre jeu.
+papa|Bravo.
+maman|Le puzzle, c'était bien.
+narrateur|Sarah touche une pièce de bois.
+narrateur|Le bois est lisse.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Barbara pose une dernière pièce. Papa range la tablette.</t>
+          <t>Sarah pose une dernière pièce. On range la tablette ? Papa range la tablette. Tu as fini de ranger ? Oui, papa. Bravo, Sarah. Merci, maman. Merci, papa. Merci, Sarah. Les cubes restent en tour. La soupe attend, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1919,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Barbara pose une dernière pièce. Papa range la tablette.</t>
+          <t>narrateur|Sarah pose une dernière pièce.
+papa|On range la tablette ?
+narrateur|Papa range la tablette.
+papa|Tu as fini de ranger ?
+enfant-f|Oui, papa.
+maman|Bravo, Sarah.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+papa|Merci, Sarah.
+narrateur|Les cubes restent en tour.
+narrateur|La soupe attend, tout près.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La dernière pièce est en place. L'écran est éteint. Oui. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La dernière pièce est en place.
+enfant-f|L'écran est éteint.
+maman|Oui.
+papa|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La soupe sent le potiron. L'odeur vient de la cuisine. Une horloge fait tic, tac. Une couverture jaune attend sur le canapé. Le tapis est un peu rêche. Dehors, le vent pousse une feuille. La feuille tape à la vitre. Un bol de bois sèche près de l'horloge. Sarah, tu sens la soupe ? Oui, maman. Ça sent le chaud. En ce moment, Sarah tient la tablette. Les couleurs dansent sur l'écran. Elles sont rouges, puis bleues. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Sarah entend. C'est fini. On va éteindre. Sarah va éteindre. Sarah éteint l'écran. L'écran devient noir. Bravo, Sarah. Tu as éteint. Tu peux prendre un autre jeu. Un autre jeu. Sarah choisit le puzzle en bois. Les pièces sentent le bois. Elles sont lisses et tièdes. Ça sent le bois. Oui. On cherche l'arbre ? Sarah cherche l'arbre. La pièce est verte. Elle rentre. Tu as su éteindre. Bravo. Papa arrive du couloir. Ses chaussettes font un bruit doux. Une pièce rentre. Bien. La pièce est à sa place. Et la maison ? La maison. La maison rentre aussi. Tu ranges la tablette ? Sarah pose la tablette. Elle continue le puzzle. Plus tard, le puzzle est fini. Fini. L'adulte dit fini, encore. On prend un autre jeu. Sarah prend les cubes. Les cubes sont rouges et bleus. Les cubes. Oui. Un autre jeu, c'est bien. Tu as fait du bon travail. La soupe sent encore le potiron.</t>
+          <t>La soupe sent le potiron. L'odeur vient de la cuisine. Une horloge fait tic, tac. Une couverture jaune attend sur le canapé. Le tapis est un peu rêche. Dehors, le vent pousse une feuille. La feuille tape à la vitre. Un bol de bois sèche près de l'horloge. Sarah, tu sens la soupe ? Oui, maman. Ça sent le chaud. En ce moment, Sarah tient la tablette. Les couleurs dansent sur l'écran. Elles sont rouges, puis bleues. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Sarah entend. C'est fini. On va éteindre. Sarah va éteindre. Sarah éteint l'écran. L'écran devient noir. Bravo, Sarah. Tu as éteint. Tu peux prendre un autre jeu. Un autre jeu. Sarah choisit le puzzle en bois. Les pièces sentent le bois. Elles sont lisses et tièdes. Ça sent le bois. Oui. On cherche l'arbre ? Sarah cherche l'arbre. La pièce est verte. Elle rentre. Tu as su éteindre. Bravo. Papa arrive du couloir. Ses chaussettes font un bruit doux. Une pièce rentre. Bien. La pièce est à sa place. Et la maison ? La maison. La maison rentre aussi. Tu ranges la tablette ? Sarah pose la tablette. Elle continue le puzzle. Plus tard, le puzzle est fini. Fini. L'adulte dit fini, encore. On prend un autre jeu. Sarah prend les cubes. Les cubes sont rouges et bleus. Les cubes. Oui. Un autre jeu, c'est bien. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Barbara est dans le salon. Elle regarde un dessin sur la tablette. Les couleurs dansent. Maman s'approche. Maman, l'adulte, dit : c'est fini. Barbara entend. Parce que l'adulte dit fini, on éteint. Barbara appuie pour &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. L'écran devient noir. Maman sourit. Maman dit : tu peux prendre un autre jeu. Barbara choisit les puzzles. Les pièces sont en bois. Elles sentent le bois. Une pièce rentre. Papa arrive. Il dit : tu as su éteindre. Barbara range la tablette. Elle continue l'autre jeu. Plus tard, papa dit aussi : c'est fini. Barbara éteint encore. Elle prend les cubes. Un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe sent le potiron. L'odeur vient de la cuisine. Une horloge fait tic, tac. Une couverture jaune attend sur le canapé. Le tapis est un peu rêche. Dehors, le vent pousse une feuille. La feuille tape à la vitre. Un bol de bois sèche près de l'horloge. Sarah, tu sens la soupe ? Oui, maman. Ça sent le chaud. En ce moment, Sarah tient la tablette. Les couleurs dansent sur l'écran. Elles sont rouges, puis bleues. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Sarah entend. C'est fini. On va éteindre. Sarah va éteindre. Sarah éteint l'écran. L'écran devient noir. Bravo, Sarah. Tu as éteint. Tu peux prendre un autre jeu. Un autre jeu. Sarah choisit le puzzle en bois. Les pièces sentent le bois. Elles sont lisses et tièdes. Ça sent le bois. Oui. On cherche l'arbre ? Sarah cherche l'arbre. La pièce est verte. Elle rentre. Tu as su éteindre. Bravo. Papa arrive du couloir. Ses chaussettes font un bruit doux. Une pièce rentre. Bien. La pièce est à sa place. Et la maison ? La maison. La maison rentre aussi. Tu ranges la tablette ? Sarah pose la tablette. Elle continue le puzzle. Plus tard, le puzzle est fini. Fini. L'adulte dit fini, encore. On prend un autre jeu. Sarah prend les cubes. Les cubes sont rouges et bleus. Les cubes. Oui. Un autre jeu, c'est bien. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1382,7 +1382,6 @@
 enfant-f|Les cubes.
 papa|Oui.
 papa|Un autre jeu, c'est bien.
-maman|Tu as fait du bon travail.
 narrateur|La soupe sent encore le potiron.</t>
         </is>
       </c>
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit fini. Que fait Barbara ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman dit fini. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1574,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,7 +1603,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Barbara a su &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Elle a choisi un autre jeu. Maman, l'adulte, a dit fini.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Sarah a éteint. Elle a choisi un autre jeu. Tu as éteint l'écran ? Oui, maman. Et après ? Un autre jeu. Bravo. Le puzzle, c'était bien. Sarah touche une pièce de bois. Le bois est lisse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,7 +1756,6 @@
 narrateur|Le bois est lisse.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Barbara pose une dernière pièce. Papa range la tablette.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose une dernière pièce. On range la tablette ? Papa range la tablette. Tu as fini de ranger ? Oui, papa. Bravo, Sarah. Merci, maman. Merci, papa. Merci, Sarah. Les cubes restent en tour. La soupe attend, tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1929,6 @@
 narrateur|La soupe attend, tout près.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La dernière pièce est en place. L'écran est éteint. Oui. Bravo, Sarah. L'histoire est finie.</t>
+          <t>La dernière pièce est en place. L'écran est éteint. Oui. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La dernière pièce est en place. L'écran est éteint. Oui. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2096,9 @@
           <t>narrateur|La dernière pièce est en place.
 enfant-f|L'écran est éteint.
 maman|Oui.
-papa|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Sarah.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, odeur de soupe, puzzle en bois</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Barbara, maman, papa</t>
+          <t>Sarah, maman, papa</t>
         </is>
       </c>
     </row>
